--- a/Data/match_medias.xlsx
+++ b/Data/match_medias.xlsx
@@ -158,6 +158,12 @@
   </x:si>
   <x:si>
     <x:t>/uploads/matchs/footballamericain/2025-2026/benjamin/2026-03-25/photos/8b559874-90c8-40e1-b834-0ccb0faa7fa0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/matchs/footballamericain/2025-2026/benjamin/2026-03-25/videos/557e4efa-ba62-42a7-8776-28e20c66a12a.MOV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Video</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1338,6 +1344,26 @@
         <x:v>46110.9858142477</x:v>
       </x:c>
     </x:row>
+    <x:row r="42" spans="1:6">
+      <x:c r="A42" s="0">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B42" s="0">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E42" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F42" s="1">
+        <x:v>46112.134347662</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/Data/match_medias.xlsx
+++ b/Data/match_medias.xlsx
@@ -164,6 +164,21 @@
   </x:si>
   <x:si>
     <x:t>Video</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/matchs/footballamericain/2025-2026/benjamin/2026-04-02/photos/e60c5d17-8825-4e63-a698-423d86176c69.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/matchs/footballamericain/2025-2026/benjamin/2026-04-02/photos/e6f102de-4648-4765-8c02-0b539a276003.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/matchs/footballamericain/2025-2026/benjamin/2026-04-02/photos/a83fea8f-b606-4956-b49f-99c7c562df7f.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/matchs/footballamericain/2025-2026/benjamin/2026-04-02/photos/7abfe968-f655-47f8-8514-56c6c3bba7f4.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/matchs/footballamericain/2025-2026/benjamin/2026-04-02/photos/56cfd665-9695-4934-9025-189752320ddb.jpg</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1364,6 +1379,106 @@
         <x:v>46112.134347662</x:v>
       </x:c>
     </x:row>
+    <x:row r="43" spans="1:6">
+      <x:c r="A43" s="0">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B43" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F43" s="1">
+        <x:v>46119.0876711574</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:6">
+      <x:c r="A44" s="0">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B44" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E44" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F44" s="1">
+        <x:v>46119.0876756019</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:6">
+      <x:c r="A45" s="0">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B45" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F45" s="1">
+        <x:v>46119.0876766435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:6">
+      <x:c r="A46" s="0">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B46" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F46" s="1">
+        <x:v>46119.087677581</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:6">
+      <x:c r="A47" s="0">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B47" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E47" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F47" s="1">
+        <x:v>46119.0876782292</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/Data/match_medias.xlsx
+++ b/Data/match_medias.xlsx
@@ -32,27 +32,6 @@
   </x:si>
   <x:si>
     <x:t>DateAjout</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/matchs/footballamericain/2025-2026/benjamin/2026-04-13/photos/3e35847e-d5b3-429e-90f2-59d59ac84976.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Photo</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/matchs/footballamericain/2025-2026/benjamin/2026-04-13/photos/1707b421-5ed4-4265-953a-9c9d74172ea3.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/matchs/footballamericain/2025-2026/benjamin/2026-04-13/photos/69094434-b53b-4445-b94d-26e4849b3753.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/matchs/footballamericain/2025-2026/benjamin/2026-04-13/photos/6ac75e9c-0b0e-49d7-a69a-b8e58dd7fe75.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/matchs/footballamericain/2025-2026/benjamin/2026-04-13/photos/1b5727d2-3119-4772-abf1-722025a73e82.jpg</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -98,20 +77,13 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="2">
+  <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="2">
+  <x:cellXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -433,106 +405,6 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:6">
-      <x:c r="A2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F2" s="1">
-        <x:v>46126.0857377431</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:6">
-      <x:c r="A3" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F3" s="1">
-        <x:v>46126.0858267477</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:6">
-      <x:c r="A4" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B4" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F4" s="1">
-        <x:v>46126.0858292014</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:6">
-      <x:c r="A5" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B5" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F5" s="1">
-        <x:v>46126.0858301273</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:6">
-      <x:c r="A6" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B6" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F6" s="1">
-        <x:v>46126.0858318981</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
